--- a/BWI/bestwine_output/bestwine_Israel.xlsx
+++ b/BWI/bestwine_output/bestwine_Israel.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA130"/>
+  <dimension ref="A1:AA131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13666,6 +13666,83 @@
       <c r="Z130" s="2" t="inlineStr"/>
       <c r="AA130" s="2" t="inlineStr"/>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>The Scottish Ltd</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>The Scottish Ltd</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>53014</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Tel Aviv</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Center District, HaSharon, Hefer Valley Regional Council</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>5 Pier Street, Emek Hefer</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>http://www.scottish.co.il</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>info@scottish.co.il</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>+972 4-617-9000</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr"/>
+      <c r="R131" s="2" t="inlineStr"/>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/scottish.co.il/</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the.scottish</t>
+        </is>
+      </c>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr"/>
+      <c r="X131" s="2" t="inlineStr"/>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Israel.xlsx
+++ b/BWI/bestwine_output/bestwine_Israel.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA131"/>
+  <dimension ref="A1:AA135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13743,6 +13743,310 @@
       <c r="Z131" s="2" t="inlineStr"/>
       <c r="AA131" s="2" t="inlineStr"/>
     </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Avi Ben</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Avi Ben</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>52950</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Jerusalem</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Jerusalem District</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>22 Yosef Rivlin Street</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>94240</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://avibenwine.com</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>avibenw@bezeqint.net</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>+972 2-625-9703</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr"/>
+      <c r="R132" s="2" t="inlineStr"/>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Avibenwine</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr"/>
+      <c r="X132" s="2" t="inlineStr"/>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Shimon Haim Foods And Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Shimon Haim Foods And Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>122637</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Eilat</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>South District, Be'er Sheva</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Harash 10</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>88000</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>https://slovatik.co.il</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>haim22051@gmail.com</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr"/>
+      <c r="P133" s="2" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr"/>
+      <c r="R133" s="2" t="inlineStr"/>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/slovatikeilat</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr"/>
+      <c r="X133" s="2" t="inlineStr"/>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Geshem Spirits</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Geshem Spirits</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>122632</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Bet Shemesh</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Jerusalem District</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>10 Hagai HaNavi Street</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://geshemspirits.com</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>info@geshemspirits.com</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr"/>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr"/>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/geshem-spirits/</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Geshem.il/</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/geshem_imports/</t>
+        </is>
+      </c>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr"/>
+      <c r="X134" s="2" t="inlineStr"/>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>The Scottish Ltd</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>The Scottish Ltd</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>53014</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Tel Aviv</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Center District, HaSharon, Hefer Valley Regional Council</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>5 Pier Street, Emek Hefer</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>http://www.scottish.co.il</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>info@scottish.co.il</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>+972 4-617-9000</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr"/>
+      <c r="R135" s="2" t="inlineStr"/>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/scottish.co.il/</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the.scottish</t>
+        </is>
+      </c>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr"/>
+      <c r="X135" s="2" t="inlineStr"/>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
